--- a/public/resources/misiones_diarias.xlsx
+++ b/public/resources/misiones_diarias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B78213-1209-4860-8DEB-DB9A6D0C3987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE855F00-FE15-4443-BDB0-A2BBFAD5629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/misiones_diarias.xlsx
+++ b/public/resources/misiones_diarias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE855F00-FE15-4443-BDB0-A2BBFAD5629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0692D54A-D2E0-48C4-8FE0-EF10635677BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/resources/misiones_diarias.xlsx
+++ b/public/resources/misiones_diarias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0692D54A-D2E0-48C4-8FE0-EF10635677BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8446F434-E379-40A9-9928-EE9EA7A59219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -60,18 +60,6 @@
     <t>desafios</t>
   </si>
   <si>
-    <t>Juega @steps partida multijugador</t>
-  </si>
-  <si>
-    <t>pvp</t>
-  </si>
-  <si>
-    <t>Completa @steps eventos cooperativos online.</t>
-  </si>
-  <si>
-    <t>evento_coop</t>
-  </si>
-  <si>
     <t>bot</t>
   </si>
   <si>
@@ -130,6 +118,12 @@
   </si>
   <si>
     <t>mejorar_cartas_v</t>
+  </si>
+  <si>
+    <t>Juega @steps partidas online.</t>
+  </si>
+  <si>
+    <t>online</t>
   </si>
 </sst>
 </file>
@@ -480,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="62.140625" bestFit="1" customWidth="1"/>
@@ -520,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2">
         <v>5</v>
@@ -540,7 +534,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2">
         <v>5</v>
@@ -574,53 +568,53 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>250</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -631,161 +625,141 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>250</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2">
-        <v>250</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>1500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" s="2">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2</v>
-      </c>
-      <c r="F15" s="2">
         <v>250</v>
       </c>
     </row>

--- a/public/resources/misiones_diarias.xlsx
+++ b/public/resources/misiones_diarias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\DC Battle Cards\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8446F434-E379-40A9-9928-EE9EA7A59219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB04F0E-4A0B-44E9-B5C3-B2760DE67B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
